--- a/LoanOfficer-A/2023/144 moirangthem naobi.xlsx
+++ b/LoanOfficer-A/2023/144 moirangthem naobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>3400</v>
+        <v>5200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>20600</v>
+        <v>18800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1406,9 +1406,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>45981</v>
+      </c>
+      <c r="C20" s="4">
+        <v>200</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1432,9 +1438,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>45981</v>
+      </c>
+      <c r="C21" s="4">
+        <v>200</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>
@@ -1458,9 +1470,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>45981</v>
+      </c>
+      <c r="C22" s="4">
+        <v>200</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
@@ -1484,9 +1502,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>45983</v>
+      </c>
+      <c r="C23" s="4">
+        <v>200</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1510,9 +1534,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>45983</v>
+      </c>
+      <c r="C24" s="4">
+        <v>200</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>
@@ -1536,9 +1566,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>45983</v>
+      </c>
+      <c r="C25" s="4">
+        <v>200</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1562,9 +1598,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>45983</v>
+      </c>
+      <c r="C26" s="4">
+        <v>200</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>
@@ -1588,9 +1630,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>45985</v>
+      </c>
+      <c r="C27" s="4">
+        <v>200</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>
@@ -1614,9 +1662,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>45985</v>
+      </c>
+      <c r="C28" s="4">
+        <v>200</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>

--- a/LoanOfficer-A/2023/144 moirangthem naobi.xlsx
+++ b/LoanOfficer-A/2023/144 moirangthem naobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>5200</v>
+        <v>8000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>18800</v>
+        <v>16000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -874,9 +874,15 @@
       <c r="E3" s="1">
         <v>31</v>
       </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="3">
+        <v>45991</v>
+      </c>
+      <c r="G3" s="4">
+        <v>200</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1</v>
+      </c>
       <c r="I3" s="1">
         <v>61</v>
       </c>
@@ -906,9 +912,15 @@
       <c r="E4" s="1">
         <v>32</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="3">
+        <v>45997</v>
+      </c>
+      <c r="G4" s="4">
+        <v>200</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
       <c r="I4" s="1">
         <v>62</v>
       </c>
@@ -938,9 +950,15 @@
       <c r="E5" s="1">
         <v>33</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="1"/>
+      <c r="F5" s="3">
+        <v>45997</v>
+      </c>
+      <c r="G5" s="4">
+        <v>200</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
       <c r="I5" s="1">
         <v>63</v>
       </c>
@@ -970,9 +988,15 @@
       <c r="E6" s="1">
         <v>34</v>
       </c>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
+      <c r="F6" s="3">
+        <v>45997</v>
+      </c>
+      <c r="G6" s="4">
+        <v>200</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
       <c r="I6" s="1">
         <v>64</v>
       </c>
@@ -1002,9 +1026,15 @@
       <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="1"/>
+      <c r="F7" s="3">
+        <v>45997</v>
+      </c>
+      <c r="G7" s="4">
+        <v>200</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
       <c r="I7" s="1">
         <v>65</v>
       </c>
@@ -1034,9 +1064,15 @@
       <c r="E8" s="1">
         <v>36</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="1"/>
+      <c r="F8" s="3">
+        <v>45997</v>
+      </c>
+      <c r="G8" s="4">
+        <v>200</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
       <c r="I8" s="1">
         <v>66</v>
       </c>
@@ -1066,9 +1102,15 @@
       <c r="E9" s="1">
         <v>37</v>
       </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="1"/>
+      <c r="F9" s="3">
+        <v>45997</v>
+      </c>
+      <c r="G9" s="4">
+        <v>200</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
       <c r="I9" s="1">
         <v>67</v>
       </c>
@@ -1098,9 +1140,15 @@
       <c r="E10" s="1">
         <v>38</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="1"/>
+      <c r="F10" s="3">
+        <v>45997</v>
+      </c>
+      <c r="G10" s="4">
+        <v>200</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
       <c r="I10" s="1">
         <v>68</v>
       </c>
@@ -1130,9 +1178,15 @@
       <c r="E11" s="1">
         <v>39</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="1"/>
+      <c r="F11" s="3">
+        <v>45997</v>
+      </c>
+      <c r="G11" s="4">
+        <v>200</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
       <c r="I11" s="1">
         <v>69</v>
       </c>
@@ -1162,9 +1216,15 @@
       <c r="E12" s="1">
         <v>40</v>
       </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="1"/>
+      <c r="F12" s="3">
+        <v>45997</v>
+      </c>
+      <c r="G12" s="4">
+        <v>200</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
       <c r="I12" s="1">
         <v>70</v>
       </c>
@@ -1694,9 +1754,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>45991</v>
+      </c>
+      <c r="C29" s="4">
+        <v>200</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1720,9 +1786,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>45991</v>
+      </c>
+      <c r="C30" s="4">
+        <v>200</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
@@ -1746,9 +1818,15 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="1"/>
+      <c r="B31" s="3">
+        <v>45991</v>
+      </c>
+      <c r="C31" s="4">
+        <v>200</v>
+      </c>
+      <c r="D31" s="1">
+        <v>1</v>
+      </c>
       <c r="E31" s="1">
         <v>59</v>
       </c>
@@ -1772,9 +1850,15 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="1"/>
+      <c r="B32" s="3">
+        <v>45991</v>
+      </c>
+      <c r="C32" s="4">
+        <v>200</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
       <c r="E32" s="1">
         <v>60</v>
       </c>

--- a/LoanOfficer-A/2023/144 moirangthem naobi.xlsx
+++ b/LoanOfficer-A/2023/144 moirangthem naobi.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>8000</v>
+        <v>9200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>16000</v>
+        <v>14800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1254,9 +1254,15 @@
       <c r="E13" s="1">
         <v>41</v>
       </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="1"/>
+      <c r="F13" s="3">
+        <v>46006</v>
+      </c>
+      <c r="G13" s="4">
+        <v>200</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
       <c r="I13" s="1">
         <v>71</v>
       </c>
@@ -1286,9 +1292,15 @@
       <c r="E14" s="1">
         <v>42</v>
       </c>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="1"/>
+      <c r="F14" s="3">
+        <v>46006</v>
+      </c>
+      <c r="G14" s="4">
+        <v>200</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
       <c r="I14" s="1">
         <v>72</v>
       </c>
@@ -1318,9 +1330,15 @@
       <c r="E15" s="1">
         <v>43</v>
       </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="1"/>
+      <c r="F15" s="3">
+        <v>46006</v>
+      </c>
+      <c r="G15" s="4">
+        <v>200</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
       <c r="I15" s="1">
         <v>73</v>
       </c>
@@ -1350,9 +1368,15 @@
       <c r="E16" s="1">
         <v>44</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="1"/>
+      <c r="F16" s="3">
+        <v>46006</v>
+      </c>
+      <c r="G16" s="4">
+        <v>200</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
       <c r="I16" s="1">
         <v>74</v>
       </c>
@@ -1382,9 +1406,15 @@
       <c r="E17" s="1">
         <v>45</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="1"/>
+      <c r="F17" s="3">
+        <v>46006</v>
+      </c>
+      <c r="G17" s="4">
+        <v>200</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
       <c r="I17" s="1">
         <v>75</v>
       </c>
@@ -1414,9 +1444,15 @@
       <c r="E18" s="1">
         <v>46</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1"/>
+      <c r="F18" s="3">
+        <v>46006</v>
+      </c>
+      <c r="G18" s="4">
+        <v>200</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
       <c r="I18" s="1">
         <v>76</v>
       </c>

--- a/LoanOfficer-A/2023/144 moirangthem naobi.xlsx
+++ b/LoanOfficer-A/2023/144 moirangthem naobi.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'MD20000.18-DEC'!$A$3:$N$32</definedName>
   </definedNames>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>9200</v>
+        <v>12000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>14800</v>
+        <v>12000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1482,9 +1482,15 @@
       <c r="E19" s="1">
         <v>47</v>
       </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="1"/>
+      <c r="F19" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G19" s="4">
+        <v>200</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
       <c r="I19" s="1">
         <v>77</v>
       </c>
@@ -1514,9 +1520,15 @@
       <c r="E20" s="1">
         <v>48</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="1"/>
+      <c r="F20" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G20" s="4">
+        <v>200</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
       <c r="I20" s="1">
         <v>78</v>
       </c>
@@ -1546,9 +1558,15 @@
       <c r="E21" s="1">
         <v>49</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
+      <c r="F21" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G21" s="4">
+        <v>200</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
       <c r="I21" s="1">
         <v>79</v>
       </c>
@@ -1578,9 +1596,15 @@
       <c r="E22" s="1">
         <v>50</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="1"/>
+      <c r="F22" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G22" s="4">
+        <v>200</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
       <c r="I22" s="1">
         <v>80</v>
       </c>
@@ -1610,9 +1634,15 @@
       <c r="E23" s="1">
         <v>51</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
+      <c r="F23" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G23" s="4">
+        <v>200</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
       <c r="I23" s="1">
         <v>81</v>
       </c>
@@ -1642,9 +1672,15 @@
       <c r="E24" s="1">
         <v>52</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="1"/>
+      <c r="F24" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G24" s="4">
+        <v>200</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
       <c r="I24" s="1">
         <v>82</v>
       </c>
@@ -1674,9 +1710,15 @@
       <c r="E25" s="1">
         <v>53</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="1"/>
+      <c r="F25" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G25" s="4">
+        <v>200</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
       <c r="I25" s="1">
         <v>83</v>
       </c>
@@ -1706,9 +1748,15 @@
       <c r="E26" s="1">
         <v>54</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="1"/>
+      <c r="F26" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G26" s="4">
+        <v>200</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
       <c r="I26" s="1">
         <v>84</v>
       </c>
@@ -1738,9 +1786,15 @@
       <c r="E27" s="1">
         <v>55</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="1"/>
+      <c r="F27" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G27" s="4">
+        <v>200</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
       <c r="I27" s="1">
         <v>85</v>
       </c>
@@ -1770,9 +1824,15 @@
       <c r="E28" s="1">
         <v>56</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="1"/>
+      <c r="F28" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G28" s="4">
+        <v>200</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
       <c r="I28" s="1">
         <v>86</v>
       </c>
@@ -1802,9 +1862,15 @@
       <c r="E29" s="1">
         <v>57</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="1"/>
+      <c r="F29" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G29" s="4">
+        <v>200</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
       <c r="I29" s="1">
         <v>87</v>
       </c>
@@ -1834,9 +1900,15 @@
       <c r="E30" s="1">
         <v>58</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="1"/>
+      <c r="F30" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G30" s="4">
+        <v>200</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
       <c r="I30" s="1">
         <v>88</v>
       </c>
@@ -1866,9 +1938,15 @@
       <c r="E31" s="1">
         <v>59</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="1"/>
+      <c r="F31" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G31" s="4">
+        <v>200</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
       <c r="I31" s="1">
         <v>89</v>
       </c>
@@ -1898,9 +1976,15 @@
       <c r="E32" s="1">
         <v>60</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="1"/>
+      <c r="F32" s="3">
+        <v>46019</v>
+      </c>
+      <c r="G32" s="4">
+        <v>200</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
       <c r="I32" s="1">
         <v>90</v>
       </c>
